--- a/results/tables/03_env_driven_taxa_clusters/table2_rda_terms_summary.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table2_rda_terms_summary.xlsx
@@ -475,24 +475,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5651395426758503</v>
+        <v>0.875440087039931</v>
       </c>
       <c r="D2" t="n">
-        <v>1.954996014998499</v>
+        <v>3.135587579983508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.032</v>
+        <v>0.003</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.4604822475488736</v>
+        <v>-0.8870438014053994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8038890491147201</v>
+        <v>0.001421567986916196</v>
       </c>
     </row>
     <row r="3">
@@ -505,43 +505,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3590027774267193</v>
+        <v>0.5241714979928096</v>
       </c>
       <c r="D3" t="n">
-        <v>1.241903894955714</v>
+        <v>1.877439316772612</v>
       </c>
       <c r="E3" t="n">
-        <v>0.249</v>
+        <v>0.028</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.4113769972096035</v>
+        <v>0.6703302454399083</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3582189858115573</v>
+        <v>-0.3500252565348506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Velocity  at bottom (m/sec)_Imputed</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3089521963620396</v>
+        <v>0.3705513568558407</v>
       </c>
       <c r="D4" t="n">
-        <v>1.068763140963329</v>
+        <v>1.327213877344657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.357</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,29 +549,29 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0.6193824780900955</v>
+        <v>0.5773446541207283</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1016030221099076</v>
+        <v>0.05888793947943283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Velocity  at bottom (m/sec)_Imputed</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2820333903275898</v>
+        <v>0.3099579526762861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9756424963227329</v>
+        <v>1.110184832882285</v>
       </c>
       <c r="E5" t="n">
-        <v>0.427</v>
+        <v>0.338</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.1723794262179527</v>
+        <v>-0.267543403483398</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1869770262984799</v>
+        <v>0.7438222997461477</v>
       </c>
     </row>
     <row r="6">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2190416193644551</v>
+        <v>0.2511226123622654</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7577340827165354</v>
+        <v>0.8994526936030247</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,29 +609,29 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.3560266750716716</v>
+        <v>-0.2127911355034832</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5073864518401274</v>
+        <v>-0.4867276026639636</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2082327137917277</v>
+        <v>0.2294545686096763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7203426674545219</v>
+        <v>0.8218436717190878</v>
       </c>
       <c r="E7" t="n">
-        <v>0.738</v>
+        <v>0.611</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-0.4652188173509023</v>
+        <v>0.2310066280648576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5027267329618662</v>
+        <v>0.5079682583046388</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/03_env_driven_taxa_clusters/table2_rda_terms_summary.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table2_rda_terms_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.875440087039931</v>
+        <v>136.4465712231137</v>
       </c>
       <c r="D2" t="n">
-        <v>3.135587579983508</v>
+        <v>6.775587496877979</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-0.8870438014053994</v>
+        <v>0.8405623114747546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001421567986916196</v>
+        <v>-0.5100551004383997</v>
       </c>
     </row>
     <row r="3">
@@ -505,43 +505,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5241714979928096</v>
+        <v>34.82730075909575</v>
       </c>
       <c r="D3" t="n">
-        <v>1.877439316772612</v>
+        <v>1.729434616480597</v>
       </c>
       <c r="E3" t="n">
-        <v>0.028</v>
+        <v>0.075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6703302454399083</v>
+        <v>-0.3258033075045645</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3500252565348506</v>
+        <v>-0.5191877302105875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Velocity  at bottom (m/sec)_Imputed</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3705513568558407</v>
+        <v>33.46604570521399</v>
       </c>
       <c r="D4" t="n">
-        <v>1.327213877344657</v>
+        <v>1.661838174587884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.122</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,29 +549,29 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5773446541207283</v>
+        <v>-0.2236117700294905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05888793947943283</v>
+        <v>-0.652292314429772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3099579526762861</v>
+        <v>23.76353463976847</v>
       </c>
       <c r="D5" t="n">
-        <v>1.110184832882285</v>
+        <v>1.180036308303854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.338</v>
+        <v>0.283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,29 +579,29 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.267543403483398</v>
+        <v>0.1511040547676921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7438222997461477</v>
+        <v>0.6553571725862285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2511226123622654</v>
+        <v>21.13425901029103</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8994526936030247</v>
+        <v>1.049473210079841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,40 +609,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.2127911355034832</v>
+        <v>-0.3040824728862437</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4867276026639636</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LOI (%)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2294545686096763</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8218436717190878</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.2310066280648576</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5079682583046388</v>
+        <v>-0.3981309310677165</v>
       </c>
     </row>
   </sheetData>
